--- a/data/stx_xlsx/VOLVb.ST.xlsx
+++ b/data/stx_xlsx/VOLVb.ST.xlsx
@@ -960,19 +960,19 @@
     <t>Bond loans</t>
   </si>
   <si>
+    <t>Other Loans (Do not use)</t>
+  </si>
+  <si>
+    <t>Current lease liabilities</t>
+  </si>
+  <si>
+    <t>Other Loans - Balancing value</t>
+  </si>
+  <si>
+    <t>Revaluation of outstanding derivatives to SEK</t>
+  </si>
+  <si>
     <t>Other Loans</t>
-  </si>
-  <si>
-    <t>Current lease liabilities</t>
-  </si>
-  <si>
-    <t>Other Loans - Balancing value</t>
-  </si>
-  <si>
-    <t>Revaluation of outstanding derivatives to SEK</t>
-  </si>
-  <si>
-    <t>Other Loans (Do not use)</t>
   </si>
   <si>
     <t>Loans</t>
@@ -16679,7 +16679,7 @@
       <c r="W112" s="15"/>
     </row>
     <row r="113" ht="15.0" customHeight="1">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="29" t="s">
         <v>313</v>
       </c>
       <c r="B113" s="15">
@@ -16973,7 +16973,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -18063,7 +18063,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="29" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B140" s="15">
         <v>59718.59</v>
@@ -18220,7 +18220,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="29" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B143" s="15">
         <v>52415.33</v>
